--- a/artfynd/A 32744-2023 artfynd.xlsx
+++ b/artfynd/A 32744-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75339021</v>
       </c>
       <c r="B2" t="n">
-        <v>108694</v>
+        <v>108704</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 32744-2023 artfynd.xlsx
+++ b/artfynd/A 32744-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75339021</v>
       </c>
       <c r="B2" t="n">
-        <v>108704</v>
+        <v>108717</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 32744-2023 artfynd.xlsx
+++ b/artfynd/A 32744-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75339021</v>
       </c>
       <c r="B2" t="n">
-        <v>108717</v>
+        <v>108718</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 32744-2023 artfynd.xlsx
+++ b/artfynd/A 32744-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75339021</v>
       </c>
       <c r="B2" t="n">
-        <v>108718</v>
+        <v>108721</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 32744-2023 artfynd.xlsx
+++ b/artfynd/A 32744-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75339021</v>
       </c>
       <c r="B2" t="n">
-        <v>108721</v>
+        <v>108727</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 32744-2023 artfynd.xlsx
+++ b/artfynd/A 32744-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>75339021</v>
       </c>
       <c r="B2" t="n">
-        <v>108727</v>
+        <v>108728</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
